--- a/forms/trg/Formulir_TRG_nnrg.xlsx
+++ b/forms/trg/Formulir_TRG_nnrg.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
